--- a/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>SNDK</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,144 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E7" s="2">
         <v>45653</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45562</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45380</v>
+      </c>
+      <c r="H7" s="2">
         <v>45289</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45198</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1695000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1876000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1883000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
+        <v>1705000</v>
+      </c>
+      <c r="H8" s="3">
         <v>1665000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1533000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1313000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1270000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1157000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="H9" s="3">
         <v>1504000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1721000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E10" s="3">
         <v>606000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>726000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>463000</v>
+      </c>
+      <c r="H10" s="3">
         <v>161000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-188000</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -805,37 +820,41 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E12" s="3">
         <v>279000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>283000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
+        <v>277000</v>
+      </c>
+      <c r="H12" s="3">
         <v>246000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>240000</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -863,66 +882,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1839000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-10000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="H14" s="3">
         <v>47000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-59000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E15" s="3">
         <v>36000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>54000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
+        <v>56000</v>
+      </c>
+      <c r="H15" s="3">
         <v>57000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>57000</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -931,66 +959,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1737000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1691000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1570000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>1626000</v>
+      </c>
+      <c r="H17" s="3">
         <v>1863000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2079000</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E18" s="3">
         <v>185000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>313000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>79000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-198000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-546000</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1002,153 +1037,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>20000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>25000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H20" s="3">
         <v>7000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E21" s="3">
         <v>201000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>342000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>130000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-148000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-488000</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="H22" s="3">
         <v>11000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>11000</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1901000</v>
+      </c>
+      <c r="E23" s="3">
         <v>173000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>267000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>54000</v>
+      </c>
+      <c r="H23" s="3">
         <v>-260000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-494000</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E24" s="3">
         <v>69000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H24" s="3">
         <v>41000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>24000</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1176,66 +1227,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1933000</v>
+      </c>
+      <c r="E26" s="3">
         <v>104000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>211000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H26" s="3">
         <v>-301000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-518000</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1933000</v>
+      </c>
+      <c r="E27" s="3">
         <v>104000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>211000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H27" s="3">
         <v>-301000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-518000</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1263,8 +1323,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1292,8 +1355,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1321,8 +1387,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1350,66 +1419,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-20000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-25000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-7000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1933000</v>
+      </c>
+      <c r="E33" s="3">
         <v>104000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>211000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H33" s="3">
         <v>-301000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-518000</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1437,71 +1515,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1933000</v>
+      </c>
+      <c r="E35" s="3">
         <v>104000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>211000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H35" s="3">
         <v>-301000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-518000</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E38" s="2">
         <v>45653</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45562</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45380</v>
+      </c>
+      <c r="H38" s="2">
         <v>45289</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45198</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1513,8 +1600,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1526,20 +1614,21 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1507000</v>
+      </c>
+      <c r="E41" s="3">
         <v>804000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>322000</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1555,8 +1644,11 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1584,20 +1676,23 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="E43" s="3">
         <v>912000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1045000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1613,20 +1708,23 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2160000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2172000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2069000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1642,20 +1740,23 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>391000</v>
+      </c>
+      <c r="E45" s="3">
         <v>568000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>952000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1671,20 +1772,23 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5090000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4456000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4388000</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,20 +1804,23 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E47" s="3">
         <v>288000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>563000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1729,20 +1836,23 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E48" s="3">
         <v>770000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>728000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,28 +1868,31 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4997000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6825000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6932000</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -1787,8 +1900,11 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1816,8 +1932,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1845,20 +1964,23 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1216000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>720000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1874,8 +1996,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1903,20 +2028,23 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12960000</v>
+      </c>
+      <c r="E54" s="3">
         <v>14234000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13890000</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,8 +2060,11 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1945,8 +2076,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1958,20 +2090,21 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>758000</v>
+      </c>
+      <c r="E57" s="3">
         <v>689000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>649000</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,28 +2120,31 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E58" s="3">
         <v>570000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>305000</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2016,20 +2152,23 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E59" s="3">
         <v>27000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>142000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,20 +2184,23 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1375000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1873000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1472000</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2074,20 +2216,23 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2123000</v>
+      </c>
+      <c r="E61" s="3">
         <v>179000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>170000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2103,20 +2248,23 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E62" s="3">
         <v>128000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2132,8 +2280,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2161,8 +2312,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2190,8 +2344,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2219,20 +2376,23 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3799000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2233000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1764000</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2248,8 +2408,11 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2261,8 +2424,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2290,8 +2454,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2319,8 +2486,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2348,8 +2518,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2377,8 +2550,11 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2406,8 +2582,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2435,8 +2614,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2464,8 +2646,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2493,37 +2678,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9161000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12001000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12126000</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3">
         <v>11439000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2551,71 +2742,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E80" s="2">
         <v>45653</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45562</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45380</v>
+      </c>
+      <c r="H80" s="2">
         <v>45289</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45198</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1933000</v>
+      </c>
+      <c r="E81" s="3">
         <v>104000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>211000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H81" s="3">
         <v>-301000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-518000</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2627,16 +2827,17 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>57000</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2656,8 +2857,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2685,8 +2889,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2714,8 +2921,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2743,8 +2953,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2772,8 +2985,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2801,37 +3017,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E89" s="3">
         <v>95000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-131000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="H89" s="3">
         <v>2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-169000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2843,37 +3065,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-48000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-67000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-75000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-24000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2901,8 +3127,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2930,37 +3159,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E94" s="3">
         <v>188000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>100000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-9000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>122000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2972,8 +3207,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3001,8 +3237,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3030,8 +3269,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3059,8 +3301,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3088,42 +3333,48 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E100" s="3">
         <v>130000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>214000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="H100" s="3">
         <v>229000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-43000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>1000</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -3146,33 +3397,39 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E102" s="3">
         <v>411000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>65000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="H102" s="3">
         <v>223000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-90000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>SNDK</t>
   </si>
@@ -656,159 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E7" s="2">
         <v>45744</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45653</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45562</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45471</v>
+      </c>
+      <c r="I7" s="2">
         <v>45380</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45289</v>
       </c>
-      <c r="I7" s="2">
-        <v>45198</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>1695000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1876000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1883000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>1705000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1665000</v>
       </c>
-      <c r="I8" s="3">
-        <v>1533000</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>1313000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1270000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1157000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
         <v>1242000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1504000</v>
       </c>
-      <c r="I9" s="3">
-        <v>1721000</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>382000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>606000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>726000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>463000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>161000</v>
       </c>
-      <c r="I10" s="3">
-        <v>-188000</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,40 +835,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>285000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>279000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>283000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>277000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>246000</v>
       </c>
-      <c r="I12" s="3">
-        <v>240000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,72 +903,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>1839000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>14000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>47000</v>
       </c>
-      <c r="I14" s="3">
-        <v>-59000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>37000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>54000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>56000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>57000</v>
       </c>
-      <c r="I15" s="3">
-        <v>57000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,72 +987,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
         <v>1737000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1691000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1570000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
         <v>1626000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1863000</v>
       </c>
-      <c r="I17" s="3">
-        <v>2079000</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-42000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>185000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>313000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>79000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-198000</v>
       </c>
-      <c r="I18" s="3">
-        <v>-546000</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,168 +1072,184 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>20000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>25000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>7000</v>
       </c>
-      <c r="I20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-15000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>201000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>342000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>130000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-148000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-488000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>9000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>11000</v>
       </c>
-      <c r="I22" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1901000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>173000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>267000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
         <v>54000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-260000</v>
       </c>
-      <c r="I23" s="3">
-        <v>-494000</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>32000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>69000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>56000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>41000</v>
       </c>
-      <c r="I24" s="3">
-        <v>24000</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1933000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>104000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>211000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
         <v>27000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-301000</v>
       </c>
-      <c r="I26" s="3">
-        <v>-518000</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1933000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>104000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>211000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>27000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-301000</v>
       </c>
-      <c r="I27" s="3">
-        <v>-518000</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1385,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,72 +1490,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-20000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-25000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-7000</v>
       </c>
-      <c r="I32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1933000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>104000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>211000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3">
         <v>27000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-301000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-518000</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1933000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>104000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>211000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3">
         <v>27000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-301000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-518000</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E38" s="2">
         <v>45744</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45653</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45562</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45471</v>
+      </c>
+      <c r="I38" s="2">
         <v>45380</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45289</v>
       </c>
-      <c r="I38" s="2">
-        <v>45198</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,23 +1702,24 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
         <v>1507000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>804000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>322000</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,8 +1735,11 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1679,23 +1770,26 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>1032000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>912000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1045000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1711,23 +1805,26 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>2160000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2172000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2069000</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1743,23 +1840,26 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>391000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>568000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>952000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,23 +1875,26 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3">
         <v>5090000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4456000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4388000</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,23 +1910,26 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>291000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>288000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>563000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1839,23 +1945,26 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>819000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>770000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>728000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,23 +1980,26 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3">
         <v>4997000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6825000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6932000</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,8 +2015,11 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,23 +2085,26 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>1333000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1216000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>720000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,8 +2120,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,23 +2155,26 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3">
         <v>12960000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14234000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13890000</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2063,8 +2190,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,23 +2222,24 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
         <v>758000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>689000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>649000</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,23 +2255,26 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
         <v>44000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>570000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>305000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2155,23 +2290,26 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>111000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>142000</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,23 +2325,26 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3">
         <v>1375000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1873000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1472000</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2219,23 +2360,26 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>2123000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>179000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>170000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2251,23 +2395,26 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>284000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>128000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>104000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,8 +2430,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,23 +2535,26 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3">
         <v>3799000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2233000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1764000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2411,8 +2570,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2521,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,16 +2725,19 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+      <c r="E72" s="3">
+        <v>-1761000</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2585,8 +2760,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,28 +2865,31 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
         <v>9161000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12001000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12126000</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I76" s="3">
-        <v>11439000</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2713,8 +2900,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E80" s="2">
         <v>45744</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45653</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45562</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45471</v>
+      </c>
+      <c r="I80" s="2">
         <v>45380</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45289</v>
       </c>
-      <c r="I80" s="2">
-        <v>45198</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1933000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>104000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>211000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
         <v>27000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-301000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-518000</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,23 +3027,24 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F83" s="3">
         <v>57000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>57000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +3060,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,40 +3235,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>26000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>95000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-131000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>-12000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2000</v>
       </c>
-      <c r="I89" s="3">
-        <v>-169000</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,40 +3287,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-67000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-29000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-75000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,40 +3390,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>404000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>188000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>100000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-9000</v>
       </c>
-      <c r="I94" s="3">
-        <v>122000</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,8 +3442,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3240,8 +3475,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,52 +3580,58 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>276000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>130000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>214000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-135000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>229000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-43000</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,36 +3650,42 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>703000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>411000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>65000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-48000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>223000</v>
       </c>
-      <c r="I102" s="3">
-        <v>-90000</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>SNDK</t>
   </si>
@@ -656,185 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46024</v>
+      </c>
+      <c r="E7" s="2">
         <v>45933</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45835</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45744</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45653</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45562</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45471</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45380</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45289</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3025000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2308000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1901000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1695000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1876000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1883000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1760000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1705000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1665000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1621000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1403000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1313000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1270000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1157000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1160000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1242000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1504000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1541000</v>
+      </c>
+      <c r="E10" s="3">
         <v>687000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>498000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>382000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>606000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>726000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>600000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>463000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>161000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,46 +861,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E12" s="3">
         <v>316000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>285000</v>
       </c>
       <c r="F12" s="3">
         <v>285000</v>
       </c>
       <c r="G12" s="3">
+        <v>285000</v>
+      </c>
+      <c r="H12" s="3">
         <v>279000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>283000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>298000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>277000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>246000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,84 +941,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E14" s="3">
         <v>16000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>33000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1839000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-10000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>47000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>36000</v>
+        <v>38000</v>
       </c>
       <c r="E15" s="3">
         <v>36000</v>
       </c>
       <c r="F15" s="3">
+        <v>36000</v>
+      </c>
+      <c r="G15" s="3">
         <v>37000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>36000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>54000</v>
       </c>
       <c r="I15" s="3">
         <v>54000</v>
       </c>
       <c r="J15" s="3">
+        <v>54000</v>
+      </c>
+      <c r="K15" s="3">
         <v>56000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>57000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,84 +1039,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1951000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2116000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1850000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1737000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1691000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1570000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1575000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1626000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1863000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="E18" s="3">
         <v>192000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>51000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-42000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>185000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>313000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>185000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>79000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-198000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,198 +1138,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E20" s="3">
         <v>28000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>20000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>997000</v>
+      </c>
+      <c r="E21" s="3">
         <v>200000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>81000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>201000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>342000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>243000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>130000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-148000</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="3">
         <v>40000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>41000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>9000</v>
       </c>
       <c r="J22" s="3">
         <v>9000</v>
       </c>
       <c r="K22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L22" s="3">
         <v>11000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>937000</v>
+      </c>
+      <c r="E23" s="3">
         <v>124000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1901000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>173000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>267000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>197000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>54000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-260000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E24" s="3">
         <v>12000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>32000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>69000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>77000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1382,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>803000</v>
+      </c>
+      <c r="E26" s="3">
         <v>112000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1933000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>104000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>211000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>120000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-301000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>803000</v>
+      </c>
+      <c r="E27" s="3">
         <v>112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1933000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>104000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>211000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>120000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-301000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1505,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1546,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1587,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,84 +1628,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-115000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-20000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>803000</v>
+      </c>
+      <c r="E33" s="3">
         <v>112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1933000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>104000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>211000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>120000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-301000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1751,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>803000</v>
+      </c>
+      <c r="E35" s="3">
         <v>112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1933000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>104000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>211000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>120000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-301000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46024</v>
+      </c>
+      <c r="E38" s="2">
         <v>45933</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45835</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45744</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45653</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45562</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45471</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45380</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45289</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1857,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,32 +1874,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1539000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1442000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1481000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1507000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>804000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>322000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>328000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,8 +1913,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1865,32 +1954,35 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1320000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1265000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1134000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1032000</v>
       </c>
-      <c r="G43" s="3">
-        <v>912000</v>
-      </c>
       <c r="H43" s="3">
+        <v>1155000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1045000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1044000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,32 +1995,35 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1907000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2079000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2160000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2172000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2069000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1955000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,32 +2036,35 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E45" s="3">
         <v>370000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>392000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>391000</v>
       </c>
-      <c r="G45" s="3">
-        <v>568000</v>
-      </c>
       <c r="H45" s="3">
+        <v>325000</v>
+      </c>
+      <c r="I45" s="3">
         <v>952000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>221000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1979,32 +2077,35 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5150000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4984000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5086000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5090000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4456000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4388000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3548000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,32 +2118,35 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E47" s="3">
         <v>261000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>295000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>291000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>288000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>563000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>510000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2055,32 +2159,35 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>834000</v>
+      </c>
+      <c r="E48" s="3">
         <v>837000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>833000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>819000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>770000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>728000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>970000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,34 +2200,37 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4995000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4998000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4999000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4997000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6825000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6932000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7207000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2131,8 +2241,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2282,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,32 +2323,35 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1272000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1263000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1347000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1333000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1216000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>720000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>684000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2245,8 +2364,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,32 +2405,35 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12998000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12749000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12985000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12960000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14234000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13890000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13506000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2446,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2465,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,32 +2482,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>869000</v>
+      </c>
+      <c r="E57" s="3">
         <v>884000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>766000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>758000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>689000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>649000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>670000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,8 +2521,11 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2400,25 +2533,25 @@
         <v>44000</v>
       </c>
       <c r="E58" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F58" s="3">
         <v>46000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>44000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>570000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>305000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>825000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2429,32 +2562,35 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E59" s="3">
         <v>57000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>87000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>111000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>142000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>226000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,32 +2603,35 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1654000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1516000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1427000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1375000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1873000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1472000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2123000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,32 +2644,35 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>769000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1519000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2022000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2123000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>179000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>170000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>171000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2543,32 +2685,35 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E62" s="3">
         <v>305000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>303000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>284000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>128000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>104000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>115000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,8 +2726,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2767,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2808,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,32 +2849,35 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3368000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3769000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3799000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2233000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1764000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2424000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +2890,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2909,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2948,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2989,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3030,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,23 +3071,26 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-869000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1672000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1784000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1761000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,8 +3112,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3153,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3194,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,32 +3235,35 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10213000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9381000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9216000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9161000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12001000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12126000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11082000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3276,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3317,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46024</v>
+      </c>
+      <c r="E80" s="2">
         <v>45933</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45835</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45744</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45653</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45562</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45471</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45380</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45289</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>803000</v>
+      </c>
+      <c r="E81" s="3">
         <v>112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1933000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>104000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>211000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>120000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-301000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,28 +3423,29 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>54000</v>
+        <v>36000</v>
       </c>
       <c r="E83" s="3">
         <v>54000</v>
       </c>
       <c r="F83" s="3">
+        <v>54000</v>
+      </c>
+      <c r="G83" s="3">
         <v>56000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>57000</v>
       </c>
       <c r="H83" s="3">
         <v>57000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>57000</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3264,8 +3462,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3503,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3544,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3585,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3626,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3667,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="E89" s="3">
         <v>488000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>94000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>26000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>95000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-131000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-130000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,46 +3727,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-45000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-44000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-48000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-29000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-75000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3807,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,46 +3848,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>404000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>188000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +3908,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +3947,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3988,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4029,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,64 +4070,70 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-758000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-515000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>276000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>130000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>214000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>85000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-135000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>229000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-1000</v>
       </c>
       <c r="F101" s="3">
         <v>-1000</v>
       </c>
       <c r="G101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,42 +4152,48 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>703000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>411000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>65000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-48000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>223000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNDK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>SNDK</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E7" s="2">
         <v>46024</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45933</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45835</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45744</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45653</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45562</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45471</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45380</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45289</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5950000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3025000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2308000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1901000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1695000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1876000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1883000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1760000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1705000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1665000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1288000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1484000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1621000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1403000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1313000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1270000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1157000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1160000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1242000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1504000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4662000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1541000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>687000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>498000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>382000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>606000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>726000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>600000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>463000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>161000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,49 +874,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E12" s="3">
         <v>327000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>316000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>285000</v>
       </c>
       <c r="G12" s="3">
         <v>285000</v>
       </c>
       <c r="H12" s="3">
+        <v>285000</v>
+      </c>
+      <c r="I12" s="3">
         <v>279000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>283000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>298000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>277000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>246000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,49 +960,55 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E14" s="3">
         <v>9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1839000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>47000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -994,40 +1016,43 @@
         <v>38000</v>
       </c>
       <c r="E15" s="3">
-        <v>36000</v>
+        <v>38000</v>
       </c>
       <c r="F15" s="3">
         <v>36000</v>
       </c>
       <c r="G15" s="3">
+        <v>36000</v>
+      </c>
+      <c r="H15" s="3">
         <v>37000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>54000</v>
       </c>
       <c r="J15" s="3">
         <v>54000</v>
       </c>
       <c r="K15" s="3">
+        <v>54000</v>
+      </c>
+      <c r="L15" s="3">
         <v>56000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>57000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,90 +1065,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1786000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1951000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2116000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1850000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1737000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1691000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1570000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1575000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1626000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1863000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4164000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1074000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>192000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>51000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>185000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>313000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>185000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>79000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-198000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,213 +1171,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>115000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>28000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>20000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4192000</v>
+      </c>
+      <c r="E21" s="3">
         <v>997000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>81000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>201000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>342000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>243000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>130000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-148000</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E22" s="3">
         <v>25000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>41000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>9000</v>
       </c>
       <c r="K22" s="3">
         <v>9000</v>
       </c>
       <c r="L22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="M22" s="3">
         <v>11000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4107000</v>
+      </c>
+      <c r="E23" s="3">
         <v>937000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>124000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1901000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>173000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>267000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>197000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>54000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-260000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E24" s="3">
         <v>134000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>32000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>69000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>56000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>77000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>41000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,90 +1433,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E26" s="3">
         <v>803000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>112000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1933000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>104000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>211000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>120000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-301000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E27" s="3">
         <v>803000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1933000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>104000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>211000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>120000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-301000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1565,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1609,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1653,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,90 +1697,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-115000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-28000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-20000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E33" s="3">
         <v>803000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1933000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>104000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>211000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>120000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-301000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,95 +1829,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E35" s="3">
         <v>803000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1933000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>104000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>211000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>120000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-301000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E38" s="2">
         <v>46024</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45933</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45835</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45744</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45653</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45562</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45471</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45380</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45289</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +1942,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,35 +1960,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3735000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1539000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1442000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1481000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1507000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>804000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>322000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>328000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,8 +2002,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1957,35 +2046,38 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2844000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1320000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1265000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1134000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1032000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1155000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1045000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1044000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1998,35 +2090,38 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2238000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1970000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1907000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2079000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2160000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2172000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2069000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1955000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,35 +2134,38 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E45" s="3">
         <v>321000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>370000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>392000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>391000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>325000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>952000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>221000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,35 +2178,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9168000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5150000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4984000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5086000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5090000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4456000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4388000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3548000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,35 +2222,38 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E47" s="3">
         <v>224000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>261000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>295000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>291000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>288000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>563000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>510000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2162,35 +2266,38 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>848000</v>
+      </c>
+      <c r="E48" s="3">
         <v>834000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>837000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>833000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>819000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>770000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>728000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>970000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,37 +2310,40 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4994000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4995000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4998000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4999000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4997000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6825000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6932000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7207000</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2354,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2398,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,35 +2442,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1272000</v>
+        <v>1128000</v>
       </c>
       <c r="E52" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1263000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1347000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1333000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1216000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>720000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>684000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2486,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,35 +2530,38 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17075000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12998000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12749000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12985000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12960000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14234000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13890000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13506000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,8 +2574,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2594,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,35 +2612,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>851000</v>
+      </c>
+      <c r="E57" s="3">
         <v>869000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>884000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>766000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>758000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>689000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>649000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>670000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,37 +2654,40 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>44000</v>
+        <v>25000</v>
       </c>
       <c r="E58" s="3">
         <v>44000</v>
       </c>
       <c r="F58" s="3">
+        <v>44000</v>
+      </c>
+      <c r="G58" s="3">
         <v>46000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>570000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>305000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>825000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2565,35 +2698,38 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>391000</v>
+      </c>
+      <c r="E59" s="3">
         <v>127000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>87000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>111000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>142000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>226000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,35 +2742,38 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1917000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1654000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1516000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1427000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1375000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1873000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1472000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2123000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,35 +2786,38 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E61" s="3">
         <v>769000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1519000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2022000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2123000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>179000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>170000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>171000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2688,35 +2830,38 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>994000</v>
+      </c>
+      <c r="E62" s="3">
         <v>340000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>305000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>303000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>284000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>128000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>104000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>115000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,8 +2874,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +2918,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +2962,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,35 +3006,38 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3298000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2785000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3368000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3769000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3799000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2233000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1764000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2424000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,8 +3050,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3070,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3112,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3156,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3200,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,26 +3244,29 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2746000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-869000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1672000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1784000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1761000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,8 +3288,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3332,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3376,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,35 +3420,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13777000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10213000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9381000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9216000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9161000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12001000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12126000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11082000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3279,8 +3464,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,95 +3508,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E80" s="2">
         <v>46024</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45933</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45835</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45744</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45653</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45562</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45471</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45380</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45289</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E81" s="3">
         <v>803000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1933000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>104000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>211000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>120000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-301000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,31 +3621,32 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E83" s="3">
         <v>36000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>54000</v>
       </c>
       <c r="F83" s="3">
         <v>54000</v>
       </c>
       <c r="G83" s="3">
+        <v>54000</v>
+      </c>
+      <c r="H83" s="3">
         <v>56000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>57000</v>
       </c>
       <c r="I83" s="3">
         <v>57000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>57000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3465,8 +3663,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3707,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3751,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3795,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +3839,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,49 +3883,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3038000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1019000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>488000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>94000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>26000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>95000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-131000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-130000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,49 +3947,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-50000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-44000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-48000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-75000</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4033,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,49 +4077,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-165000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>404000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>188000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4141,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3950,8 +4183,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4227,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4271,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,70 +4315,76 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-752000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-758000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-515000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>276000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>130000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>214000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>85000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-135000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>229000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-1000</v>
       </c>
       <c r="G101" s="3">
         <v>-1000</v>
       </c>
       <c r="H101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4155,45 +4403,51 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2196000</v>
+      </c>
+      <c r="E102" s="3">
         <v>97000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>703000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>411000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>65000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-49000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-48000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>223000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>
